--- a/src/data/tables/Sales_FAQs.xlsx
+++ b/src/data/tables/Sales_FAQs.xlsx
@@ -7,7 +7,10 @@
     <workbookView windowWidth="27040" windowHeight="11020"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="节点常见问题" sheetId="2" r:id="rId2"/>
+    <sheet name="通用常见问题" sheetId="3" r:id="rId3"/>
+    <sheet name="产品基础问题" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="318">
   <si>
     <t>常见问题</t>
   </si>
@@ -35,7 +38,1847 @@
     <t>话术建议</t>
   </si>
   <si>
+    <t>节点</t>
+  </si>
+  <si>
+    <t>破冰标准话术</t>
+  </si>
+  <si>
+    <t>结尾确定时间，下痛点话术</t>
+  </si>
+  <si>
+    <t>常问问题</t>
+  </si>
+  <si>
     <t>我和孩子商量商量，孩子愿意就来，不愿意也没办法</t>
+  </si>
+  <si>
+    <r>
+      <t>判断家长是否敷衍：是的话，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>反思是否挖到了家长的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>需求</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>？</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>案例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是否吸引？是否足够</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>专业</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>？</t>
+    </r>
+  </si>
+  <si>
+    <t>月考</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>您好**妈妈/爸爸，我是***学校对面全科辅导*老师，昨晚在学校门口跟孩子送了思维导图，您回家给孩子贴上了吗？之前给孩子送了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月考冲刺/考后补弱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一次课，可以免费提升弱科。咱孩子平时成绩咋样？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你给孩子说说，带着孩子过来，明天下午2点没问题吧？明天见，抓紧给孩子找找问题，马上就要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月考</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>了</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>不敷衍，参考话术一：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>孩子现在还不懂事，家长咱需要正向引导，鼓励他往好的方向去走，等咱老了生病了，自己不愿意去医院孩子就不带着去了，你是不是也希望孩子哄哄你劝劝你，如果是单纯不愿意到店学的，可以说我们是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>随时学</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，可以在家利用碎片时间学习。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>期中考</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>您好**妈妈/爸爸，我是***学校对面全科辅导*老师，昨晚在学校门口跟孩子送了思维导图，您回家给孩子贴上了吗？之前给孩子送了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>期中冲刺/考后补弱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一次课，可以免费提升弱科。咱孩子平时成绩咋样？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你给孩子说说，带着孩子过来，明天下午3点没问题吧？明天见，抓紧给孩子找找问题，马上就要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>期中考</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>了</t>
+    </r>
+  </si>
+  <si>
+    <t>马上放假了，等等吧，等放假了再过去？
+你们暑假班怎么收费的？</t>
+  </si>
+  <si>
+    <r>
+      <t>不敷衍，参考话术二：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>家长的态度决定孩子的成绩，你非常愿意让他来，你就能说动他。如果你家孩子比较听话，你带着来就行；要是比较倔强的，你就说带他出来转转看看，哄着他来，劝着他来</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，咋也不一定报，先看看喜不喜欢。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、我们周末来的孩子很多，最近他们学到那个勾股定理了，不会的周六有时间就过来学习了，放假就是超越的时间，往后</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>拖一周就是拖一周的内容</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，马上又考试了，得重视起来了。</t>
+    </r>
+  </si>
+  <si>
+    <t>期末考</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>您好**妈妈/爸爸，我是***学校对面全科辅导*老师，昨晚在学校门口跟孩子送了思维导图，您回家给孩子贴上了吗？之前给孩子送了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>期末冲刺/考后补弱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一次课，可以免费提升弱科。咱孩子平时成绩咋样？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你给孩子说说，带着孩子过来，明天下午4点没问题吧？明天见，抓紧给孩子找找问题，马上就要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>期末考</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>了</t>
+    </r>
+  </si>
+  <si>
+    <t>你们暑假班怎么收费的？
+刚考完，让孩子休息2天？
+马上放假了，等等吧，等放假了再过去？</t>
+  </si>
+  <si>
+    <t>我平时太忙了，也没时间管孩子（一直推托带孩子到店体验）</t>
+  </si>
+  <si>
+    <r>
+      <t>举例实际客户：我有一个客户是县里的干部，工作也特别忙没时间照看孩子，我就说你现在还没退休但如果等过几年退休了，你当再大的官你退休了啥也不是，是不是；但你把孩子培养好了，孩子就是你自己的未来，工作离了你照样转，把孩子培养好了才是一家人一生的幸福，是不是这个道理；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>现在孩子小需要你陪伴管理时你不管，等老了你需要孩子的时候，他也是忙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>带来体验1个小时就够了，先安排给孩子的学习时间</t>
+    </r>
+  </si>
+  <si>
+    <t>开学考</t>
+  </si>
+  <si>
+    <t>您好家长，我是***学校对面全科辅导*老师，咱这周末有一对一的课程，可以免费提升弱科。咱孩子平时成绩咋样？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你给孩子说说，带着孩子过来，明天下午5点没问题吧？明天见，抓紧给孩子找找问题，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>开学考完，马上就要月考了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，抓紧上前提提成绩</t>
+    </r>
+  </si>
+  <si>
+    <t>孩子不愿意学</t>
+  </si>
+  <si>
+    <r>
+      <t>先了解孩子学情基本都是成绩一般的学生：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>孩子应该之前有听不懂的，落下的越多，越不愿意学。上课的时候老师讲了一遍没听懂，咋办？咱能让老师再单独给讲第二遍第三遍吗？我们课程可以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>重复听反复听</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，不用担心接受慢和前置知识点不会没人帮助的的问题。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你给孩子说说，带着孩子过来，明天下午2点没问题吧？明天见，抓紧给孩子找找问题，马上就要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月考</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>了，抓紧上前提提成绩</t>
+    </r>
+  </si>
+  <si>
+    <t>没有时间再学了，课业太多</t>
+  </si>
+  <si>
+    <r>
+      <t>确实现在孩子作业都不少，时间这么紧这么累还是有成绩不理想的，咱更应该给孩子找个高效的学习方法，把成绩提上去。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>咱之前上的辅导班一节课大概是1小时吧，这一小时老师讲的都是你想学的知识点吗？都是你薄弱的知识点吗？我们</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按点听课功能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，针对性强哪里不会听哪里，每天抽出10-20分钟的碎片化时间就可以解决当天不会的知识点问题。还能提高写作业的速度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你给孩子说说，带着孩子过来，明天下午3点没问题吧？明天见，抓紧给孩子找找问题，马上就要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>期中考</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>了，抓紧上前提提成绩</t>
+    </r>
+  </si>
+  <si>
+    <t>你们是网课吗，网课效果不好</t>
+  </si>
+  <si>
+    <r>
+      <t>咱们这个网课和平时上的网课不一样，我们这个是因人施教，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分层教学</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的，一人一层次一人一方案，针对性解决孩子问题；找辅导的目的就是解决孩子的问题，家长不要纠结方式。不喜欢线上是家长您的认知，您不能把孩子限制到您的认知里，这样您永远是您家里认知的天花板。您是不是希望孩子长大比您优秀？现在是AI时代了，再这么传统就跟不上社会发展了。您可以比较，但不能不试就拒绝。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成绩好的：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>孩子上的辅导班，都是好学生吗？老师讲课是针对好学生讲知识拓展吗？显然还要照顾其它孩子，就导致咱吃家孩子吃不饱，浪费了一些学习时间。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成绩中等的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：孩子上的哪个层次的辅导班？咱孩子成绩中等，也不是都不会吧？主要还应该聚焦咱不会的章节知识点合理规划学习。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成绩差的：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>孩子上的辅导班以讲基础为主吗？是针对咱家孩子这个层次的吗？大部分还是要按照中等左右以上设定课程方案，咱长期处在追赶的状态，心态疲惫时间长了成绩不但提不上去，也容易失去兴趣。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你给孩子说说，带着孩子过来，明天下午4点没问题吧？明天见，抓紧给孩子找找问题，马上就要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>期末考</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>了，抓紧上前提提成绩</t>
+    </r>
+  </si>
+  <si>
+    <t>买了之后，孩子不愿意学怎么办？</t>
+  </si>
+  <si>
+    <r>
+      <t>1、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>孩子哪有天生不愿意学习、不愿意进步的?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>只要我们找到孩子的问题针对性解让，那孩子有信心了，他就能愿意学习，他就能提升。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你前期叫孩子来店里学习两周，给孩子培养学习习惯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。等他听懂了会做题了，提升学习效率了，尝到进步的甜头了，他就愿意学了，就主动了。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、越拖就越导致孩子上课越来越不懂，越来越跟不上，基础愈加薄弱，写作业时间越来越长，越来越费劲，越不愿意学。慢慢的就形成恶性循环了，导致孩子彻底失去学习兴趣和动力。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4、当然，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>家长你愿意的话也可以陪孩子学一段时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，有1个月就足够给孩子培养好的学习习惯了。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>寒暑假</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你给孩子说说，带着孩子过来，明天下午9点没问题吧？明天见，抓紧给孩子找找问题，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>下个学期整体学科的难度也会增加，上个学期的内容没掌握，下学期很有可能彻底跟不上，开学考没考好也影响孩子的自信心</t>
+    </r>
+  </si>
+  <si>
+    <t>你们暑假班怎么收费的？</t>
+  </si>
+  <si>
+    <t>孩子比较叛逆，不听劝呀</t>
+  </si>
+  <si>
+    <t>现在很多孩子都比较叛逆，家长要好好引导，但不是一直唠叨。要坚定你的态度，家长的态度，决定孩子的成绩。孩子吃喝拉撒都靠你，不可能完全不听劝。你带着他出来转转，也不一定要报课，让他来看看，喜不喜欢，我跟他聊聊。</t>
+  </si>
+  <si>
+    <t>核心特点</t>
+  </si>
+  <si>
+    <t>标准邀约话术</t>
+  </si>
+  <si>
+    <t>我们报了辅导班了</t>
+  </si>
+  <si>
+    <r>
+      <t>1、其他的补习效果怎么样？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、家长花了这个钱，一定要时刻关注是不是起到效果了，哪怕没有考试，也要看看孩子进展怎么样？会不会做作业了，上课是不是比以前听得懂了，问问学校老师，状态好些了没有？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、你也可以听听我们这个课，让孩子对比一些，多一种方式，多一种可能性。有对比才能看到好赖。</t>
+    </r>
+  </si>
+  <si>
+    <t>科目多（7 科）、知识点杂但不难；初中起点；重在建立信心与兴趣</t>
+  </si>
+  <si>
+    <t>孩子不适应初中节奏怎么办？怕跟不上、怕掉队</t>
+  </si>
+  <si>
+    <t>初一最关键是适应节奏、打牢基础、建立自信。我们 帮孩子梳理知识点、培养习惯，免费做学情诊断，您看约 20 分钟体验一下？</t>
+  </si>
+  <si>
+    <t>你这个对视力不好</t>
+  </si>
+  <si>
+    <r>
+      <t>1、认可担心：戴眼镜已经成为一种社会普遍现象。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、讲事实，戳痛点：在地里干农活的、工地搬砖的没有戴眼镜的，坐办公室、轻松赚钱的几乎都是戴眼镜的，家长，你选哪个？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3、给解决方案：我们的学习机是类纸屏，带护眼功能。</t>
+    </r>
+  </si>
+  <si>
+    <t>8 科、难度陡增、进度快；两极分化最严重；80% 成绩下滑从初二开始；新增物理</t>
+  </si>
+  <si>
+    <t>孩子成绩突然下滑怎么办？物理跟不上怎么办？</t>
+  </si>
+  <si>
+    <t>初二是分水岭，不抓紧就掉队！我们帮孩子补薄弱、稳理科基础，免费做薄弱点检测，20 分钟出方案，我帮您约个时间？</t>
+  </si>
+  <si>
+    <t>和孩子商量商量，不想给他增加学习负担，现在学习已经很累了</t>
+  </si>
+  <si>
+    <t>你给孩子买课，帮他提高，这还商量啥？你得和孩子说：别的家长都舍不得给孩子买课，舍不得花这个钱，妈妈多爱你呢，我直接给你买了。我看你做题做到XX点，这么晚我都心疼，妈妈也帮不了你别的，你用这个课估计很快就写完作业了。你得无条件相信孩子。再说了，孩子在这都说可以、想上了，你还一直追着问，你自己想想多有压力啊。你想听孩子烦躁了说"不学了"啊？那是钱的事情吗？那孩子上学这条路就断了。趁他有兴趣，咱做家长就无条件支持、相信自己孩子才行。</t>
+  </si>
+  <si>
+    <t>进度极快、一学期学一年内容；中考冲刺；新增化学；考点多、复习紧</t>
+  </si>
+  <si>
+    <t>能不能考上重点？时间紧怎么高效复习？</t>
+  </si>
+  <si>
+    <t>初三是中考冲刺关键期，我们精准查漏、抓考点、提速提分，免费做中考学情规划，我帮您约个体验名额？</t>
+  </si>
+  <si>
+    <t>这个课和我们考的题不一样</t>
+  </si>
+  <si>
+    <r>
+      <t>任何一次考试都和你平时不一样，来我们这学习不是做哪个题的也不是学哪一科的，是感受我们这边老师的上课方式，能不能帮到你；主要是学的学习方法，那么多题永远也做不完，学的是老师的思路及思维拓展，我们课上有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“简单好方法”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，正好解决学习浮于表面，错题不反思总结，一错再错或稍变换题型就不会了的情况</t>
+    </r>
+  </si>
+  <si>
+    <t>9 科、难度跨度大、进度快；高中基础分水岭；知识占高考 70%；衔接弱易崩盘</t>
+  </si>
+  <si>
+    <t>孩子高中跟不上怎么办？怕高一塌腰影响整个高中</t>
+  </si>
+  <si>
+    <t>高一决定高中三年走向！知识占高考 70%，我们帮孩子衔接过渡、夯实基础，免费做高中学习规划，可以过来体验一下</t>
+  </si>
+  <si>
+    <t>在学校/辅导班老师看着都不学呢，这网课更不学了</t>
+  </si>
+  <si>
+    <r>
+      <t>家长你可以问问孩子：孩子在辅导班或者课堂上，老师一节课提问咱几次？这一天下来是不是会出现几次走神？这没办法，老师课堂上照顾不了这么多孩子，没办法及时发现和及时提醒，所以看似有老师看着，实际是没办法时时关注到每一个孩子的。咱们的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要点小测</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，就相当于课堂提问老师，可以时时关注咱孩子，咱们针对家长也有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>学情报告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，你只要有网随时随地可以了解孩子学习的情况。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>难度最大、综合性最强；衔接高一；赶进度、5 月结课；断层明显、偏科严重</t>
+  </si>
+  <si>
+    <t>孩子偏科怎么办？怕跟不上一轮复习</t>
+  </si>
+  <si>
+    <t>高二是断层期、焦虑最强，我们帮孩子补弱科、固高一基础、提前适应复习节奏，免费做薄弱科诊断，我帮您约一下？</t>
+  </si>
+  <si>
+    <t>放学晚/放假时间少，没时间听这么多课</t>
+  </si>
+  <si>
+    <r>
+      <t>咱们课程就是个百宝箱/字典，只需要去听课上没听懂的，课上没听懂的都能找到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>比想听的找不到好呀，像咱们花二三十万买辆车，也不是天天开，有需要的才开呀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>比如家里一天做四个菜，也不用全吃呀，选自己想吃的就行，那就很值了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>——我们的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按点听课</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，哪里不会听哪里。我们的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同类题</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，做一题会一类题，都是高效的学习方法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>全年复习、进度极快；一轮补基础、二轮专题、三轮冲刺；期中是一轮大检验</t>
+  </si>
+  <si>
+    <t>一轮复习跟不上怎么办？怎么快速提分、冲名校</t>
+  </si>
+  <si>
+    <t>高三一轮是最后补基础机会，期中暴露的问题必须立刻解决！我们 AI 查漏、抓高频考点，免费做冲刺规划，我帮您约一下？</t>
+  </si>
+  <si>
+    <t>孩子成绩比较好，不需要再补了</t>
+  </si>
+  <si>
+    <r>
+      <t>我们这个不是补课，如果成绩比较优秀的话，建议重点学数学物理，数学是重中之重，今年也出政策了如数学特别优秀可以破格录取，咱这个课不是让孩子更累是让孩子学习更轻松；另外我们</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分层教学</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，成绩比较优异的学生让他多做做满分冲刺的题，题型见的多了难题见的多了，孩子思维能力也提升了到了高中就更有潜力；初三的尖子生可以提前学高中课程，尖子生到了快班后孩子提前预习了会学更好；</t>
+    </r>
+  </si>
+  <si>
+    <t>这么学习有效果吗？</t>
+  </si>
+  <si>
+    <r>
+      <t>①提升成绩是一个过程，成绩和学习方法、学习习惯都有关系，所以不能只改变方法或者只改变习惯，一定要坚定信心，既要改变方法又要改变习惯——使用简而优闯关练学习机，从方法上来说，简而优的学习方法是选练听闯追五步法、按一对一的流程学：学管师帮学生规划内容；孩子练题的时候和闯关一样、很有趣，同时把知识和题型结合得更紧密，学知识点很快就能会用；不会的题有精英老师的视频讲解、错题再次练同类题闯关、不断补闯关追错。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从习惯上来说，原来做题少现在要尽力做题，因为题的难度本身适合学生、闯关的过程也比较有趣有成就感、不断补闯关把一节的知识点典型题会做了，做题的时候认真写步骤需要拍照的时候认真拍照上传。好习惯在好的流程里也慢慢养成了。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="SimSun"/>
+        <charset val="134"/>
+      </rPr>
+      <t>②目前大多数坚持1个月以上的同学，都有进步，希望你也能加入进步的队伍。</t>
+    </r>
+  </si>
+  <si>
+    <t>怕下滑、要拔高、冲排名、重效率、时间宝贵</t>
+  </si>
+  <si>
+    <t>1. 能培优 / 冲刺吗？2. 内容会不会太简单？3. 效果怎么样？4. 会不会浪费时间？</t>
+  </si>
+  <si>
+    <t>我们不做低水平重复，专门帮优生查漏补缺、保持优势、冲刺更高排名，只抓薄弱点和难题，高效省时间。我帮您约个免费诊断，20 分钟就够，您看今天还是明天？</t>
+  </si>
+  <si>
+    <t>你们哪里来的我电话？</t>
+  </si>
+  <si>
+    <t>应该是小学在学校门口做宣传时，之前留的。我们是做弱课提升的，主要就是想给孩子提升成绩的。您要有需求联系我哈，要是没有需求，真是抱歉了，打扰您了哈。您也可以记一下我电话，有需求了联系我，我们专门做初高中辅导19年了，在咱当地也是相对最专业的哈。</t>
+  </si>
+  <si>
+    <t>最焦虑、想提分、瓶颈明显、忽上忽下、不自觉、最易成交</t>
+  </si>
+  <si>
+    <t>1. 怎么突破瓶颈？2. 多久能提分？3. 薄弱点怎么补？4. 孩子不自觉你们管吗？</t>
+  </si>
+  <si>
+    <t>中等生是最好提分的！我们用 AI精准找薄弱、针对性练、盯紧学习习惯，帮孩子快速稳住分数、冲进上游。现在正好赶上月考 / 期中，我帮您约个免费检测，20 分钟出方案。</t>
+  </si>
+  <si>
+    <t>孩子时间紧、累，没有时间学习/作业多，没时间怎么办？</t>
+  </si>
+  <si>
+    <t>主要问题是孩子时间这么紧、这么累，成绩不理想啊。这么辛苦咱们是为了有个好前程吧，不是为了现在上学辛苦以后工作还辛苦。他没有找到适合自己的学习方法，都白白辛苦了。（再分析我们的分层教学及其他孩子使用的案例及我们的按点听课功能）</t>
+  </si>
+  <si>
+    <t>基础弱、没兴趣、怕跟不上、怕花钱没用、怕孩子抵触、缺信心</t>
+  </si>
+  <si>
+    <t>1. 基础差能教吗？2. 孩子不爱学怎么办？3. 能跟得上吗？4. 会不会打击自信？</t>
+  </si>
+  <si>
+    <t>我们专门帮基础弱的孩子从简单入手、补牢基础、提升兴趣，一步步来，不打击信心，让孩子慢慢跟上。您带孩子过来免费体验一下，轻松无压力，我帮您约个时间。</t>
+  </si>
+  <si>
+    <t>时间紧，没时间听，担心给孩子增加负担</t>
+  </si>
+  <si>
+    <t>给孩子报名是帮孩子解决问题的，不是增加负担的。有问题了再用，可以很及时地解决问题、做学习补充，没有问题的时候就可以不用啊。（再分析其他孩子使用的案例及我们的按点听课功能）</t>
+  </si>
+  <si>
+    <t>常问问题 / 拒绝语</t>
+  </si>
+  <si>
+    <t>标准应对话术</t>
+  </si>
+  <si>
+    <t>课太多听不过来，想报单科</t>
+  </si>
+  <si>
+    <t>新华字典那么多字，一辈子咱也看不过来呀，咱就是得哪里不会听哪里。那还能学校学一遍，来店再学一遍吗？孩子时间也不允许啊。你现在这科（想报的那科）有问题，其他科还等出问题再学吗？就是其他科考满分，以后还有新知识点呢，哪可能没有新学习的需要呢？再说现在单科一年1400/1800元，一年才多少钱（展开算数字），买三科就送全年了，真是没有人买单科的。</t>
+  </si>
+  <si>
+    <t>孩子成绩一般 / 下滑，家长焦虑，愿意为提分付费</t>
+  </si>
+  <si>
+    <t>1. 你们怎么帮孩子提分？2. 多久能看到效果？3. 一个班多少人？老师负责吗？</t>
+  </si>
+  <si>
+    <t>直接讲 AI 查漏、针对性练、盯习惯，强调月考 / 期中快速提分</t>
+  </si>
+  <si>
+    <t>课程这么多，没时间听完，花的钱感觉浪费了</t>
+  </si>
+  <si>
+    <t>咱们课程就是个百宝箱/字典，只需要去听课上没听懂的，课上没听懂的都能找到，比想听的找不到好呀。像咱们花二三十万买辆车，也不是天天开，有需要才开呀。比如家里一天做四个菜，也不用全吃呀，选自己想吃的就行，那就很值了。（再分析其他孩子使用的案例及我们的按点听课功能）</t>
+  </si>
+  <si>
+    <t>学历高、冷静、问得细、不冲动</t>
+  </si>
+  <si>
+    <t>1. 你们和补习班有什么区别？2. AI 到底怎么用？3. 价格多少？有效果保证吗？4. 师资什么水平？</t>
+  </si>
+  <si>
+    <t>讲数据、方法、流程、真实案例，少煽情，多给安全感</t>
+  </si>
+  <si>
+    <t>你们这老师讲的和我们学校老师讲的也没啥区别</t>
+  </si>
+  <si>
+    <t>跟你们老师讲的差不多，说明我们课程是跟你们学校完全同步的。你看我们的老师都是老师的老师，你们学校的老师都是用我们课程备课。重要的是学校老师讲的你这不是没听懂吗？学校老师不会再给你重复讲了，正好用我们的课程再补充没听懂的，我们的课程可以重复听没听懂的。</t>
+  </si>
+  <si>
+    <t>一开口就说忙、作业多、排满课</t>
+  </si>
+  <si>
+    <t>1. 我们没时间，算了2. 周末补课排满了3. 太远不方便</t>
+  </si>
+  <si>
+    <t>不纠缠、不解释：20 分钟体验，不耽误，我帮您占个名额</t>
+  </si>
+  <si>
+    <t>我们就要找线下1对1/线下的老师？</t>
+  </si>
+  <si>
+    <t>线下1对1效果确实不错，你不能把线下1对1带回家呀，不能随时给你解决问题的。线下一周就1-2个小时解决不了你的问题，你现在的成绩不好就是问题积累了。我们的课程可以每天都用，当天有听不懂的当天拿出10分钟听一下就解决了。</t>
+  </si>
+  <si>
+    <t>反感推销、怕套路、怕被缠</t>
+  </si>
+  <si>
+    <t>1. 你们是不是要卖课？2. 免费是不是有套路？3. 不用了，别再打</t>
+  </si>
+  <si>
+    <t>先给安全感：免费、不强制、不推销、20 分钟就走</t>
+  </si>
+  <si>
+    <t>考虑线下辅导怎么办？</t>
+  </si>
+  <si>
+    <t>你今天学XX（某学生正在学的知识点）对吗？你要是正好这个知识点有问题，辅导班今天就马上给你讲这个知识点吗？你问题不就是得立刻解决吗？（+前后置知识点展开说）</t>
+  </si>
+  <si>
+    <t>不拒绝不答应、一直拖、怕选错</t>
+  </si>
+  <si>
+    <t>1. 我再想想 / 和孩子商量2. 有没有效果？别家差不多3. 先不着急，等等看</t>
+  </si>
+  <si>
+    <t>给限时名额 + 考试节点紧迫感，推动快速做决定</t>
+  </si>
+  <si>
+    <t>先报一科吧，那么多也没时间学</t>
+  </si>
+  <si>
+    <t>初一就有7科，每天都有听不懂的情况。我们这个课程在平时（周一到周五）就像一本会说话的字典，孩子哪里不会就听哪里，不是每个科目都是学生全部去学，而是查缺补漏。这个课程不是说买回去后天天让孩子学、每天都要让孩子学多长时间，就是有事的时候、遇到问题的时候，我们有这个课程能帮学生解决问题，并不是给你增加任务。（然后给家长看其他同年级学生的听课报告）</t>
+  </si>
+  <si>
+    <t>一上来问价、关注划算、怕贵</t>
+  </si>
+  <si>
+    <t>1. 多少钱一节课？2. 贵不贵？有优惠吗？3. 能不能先体验再谈钱？</t>
+  </si>
+  <si>
+    <t>不直接报价，引导到店：先体验看效果，再按孩子情况给方案，价格透明</t>
+  </si>
+  <si>
+    <t>任何一次考试都和你平时不一样。来我们这学习不是做哪个题的，也不是学哪一科的，是感受我们这边老师的上课方式，能不能帮到你。主要是学学习方法，那么多题永远也做不完，学的是我们这边老师的上课理念和流程及拓宽思维。</t>
+  </si>
+  <si>
+    <t>参考sheet3</t>
+  </si>
+  <si>
+    <t>能保证效果吗，能的话我就来，这里报名能保证提成绩吗？</t>
+  </si>
+  <si>
+    <t>不需要正面回答，家长可以反问：咱孩子是不是成绩已经落下了？刚了解完咱们的课程，家长你是不是也感觉到了课程很适合孩子？就像您生病了，100%确定这个药对你的症状，如果拿了药您持续服用、正确服用，肯定能治好；如果拿回去后您嫌苦不吃，肯定治不好。所以，我们和您一起鼓励孩子，正确持续地使用，一定能提升。</t>
+  </si>
+  <si>
+    <t>我家孩子觉得太贵了（孩子比较懂事）</t>
+  </si>
+  <si>
+    <t>教育是投资不是消费。孩子要是考的分数高，那是省多少学费啊！民办大学、公立大学学费差出去几万块钱。（本地大家普遍知道的大学）学费才XX钱，你看咱XX私立大学学费要XX呢。孩子是真懂事，但是要想真的孝顺父母，不就是得咱好好学，后期去好大学才能找好工作、多赚钱吗？这个事情咱家长得给孩子定啊，这么懂事的孩子别耽误了。</t>
+  </si>
+  <si>
+    <t>已经报辅导班了</t>
+  </si>
+  <si>
+    <t>（不要直接挂电话，这些客户都是重视教育的，当下不报后续也有可能报，多跟家长聊聊）孩子报的哪个机构？报的哪几科？一个班几个孩子？（了解辅导班形式、结束时间、报的科目、开学是否走读等，方便后续跟进以及跟其他家长对比）高中不比初中，副科难度也挺大的，而且我们孩子后续高一选哪几科也不确定呢，我们可以送几节副课给孩子，对比着学习几天看看效果。您有时间可以带孩子过来试试看。我们这边效果确实很好，去年有一个叫XXX的学生，中考也是刚刚上一中的分数线，暑假在我们这里学的，第一次月考就到班级13名，全校XXX名了。还有一个叫XXX的学生，也是中考分数很一般，暑假在我们这里学得很好，第一次月考就到班级第9名，现在已经稳定班级5、6名的样子，很不错了。如果维持下去的话，考大学就没问题了。现在孩子上高中了，不比初中，不能随便报个班就算。要给孩子找好的老师，我们这边都是名师授课。你像今年的高考数学全国一卷，我们原题压中了105分，其他科目也压中很多题，语文作文、英语作文都是原题压中的。（这样的客户可能暂时拿不下，或者邀约到店难度大，要了解辅导班结束时间，结束前留意再跟进）</t>
+  </si>
+  <si>
+    <t>同学们有报线下班的，孩子也想报线下辅导班</t>
+  </si>
+  <si>
+    <r>
+      <t>价格对比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：辅导班暑期22天需要3000-4000元（根据本地情况说）。我们5000元含1个暑期班、1个寒假班，平时国庆及周末节假日也可以及时查漏补缺。9600元，3个暑假+3个寒假+平时所有节假日周末，6个假期辅导班价格2万+，我们只需要9600元。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>效果对比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：价格还不是最重要的，效果最重要。我们这个是因人施教，一人一层次一人一方案，针对性解决孩子问题。高中知识点难，很多预习一遍是听不透的，简单一百可以针对听不懂的听2-3遍。辅导班22天学4科，每科预习3章，家长你想想一周学一科3章，孩子怎么能听懂啊，浪费了钱也耽误了孩子的时间。</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上课时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：辅导班22天，22天后在家刷手机？找同学玩？心又散了。我们的课程，孩子可以预习到军训。虽然不能让孩子太累，每天学习3-4小时休息3-4小时，不至于心散了。</t>
+    </r>
+  </si>
+  <si>
+    <t>对应标准邀约话术</t>
+  </si>
+  <si>
+    <t>春季前后置知识点话术</t>
+  </si>
+  <si>
+    <t>刚考完，让孩子休息2天？</t>
+  </si>
+  <si>
+    <t>刚考完确实很辛苦也紧张的，应该好好放松放松。不过，你可以先给孩子看看，多选选对比对比。而且现在很多辅导班都报满了，建议你先给孩子看看，合适的话先给孩子预留一个位置。而且学生上高中了，跟初中完全不一样，孩子的状态和习惯可不能放松太久，久了就很难再抬起来。高中成绩好坏高一很关键：高一成绩好基础好高二学起来轻松。高一成绩好坏这个暑假很关键：暑假预习了开学测试成绩好了可以得到老师的关注，自己也有自信。你可以先过来看看，我们给孩子做个规划。昨天二中的王XX同学，不知道你认不认识，他二模全校第17名，成绩非常优秀，这次考得也很不错。她妈妈昨天带她来试听了两节新高一的课程，当场感觉高中的课很有难度，现场就把数理化英四个科目的预习规划做好了。提前做好规划，让孩子劳逸结合，适度放松。这个暑假肯定是要提前学才行，高中难度确实很大，可以先来了解一下，避免后续报不上或者盲目报班，花了钱没有效果。</t>
+  </si>
+  <si>
+    <t>一、初一</t>
+  </si>
+  <si>
+    <t>我们价格很实惠，比一般的辅导班要实惠很多，而且效果很好。去年我们总共有200多个学员，像一中就有120多个学生，高一第一次月考的平均分比全校高50多分。有一个叫孙柏彬的学生，去年中考也是刚刚上一中的分数线，暑假在我们这里学的，第一次月考就到班级13名，全校XXX名了。确实预习效果很好，暑假预习一遍，学校教的时候就是复习了。别人都搞不懂的时候你是复习，成绩肯定差不了。如果家长追问价格：综合一年也就4000多点。</t>
+  </si>
+  <si>
+    <t>1.初一数学</t>
+  </si>
+  <si>
+    <t>马上放假了，等等吧，等放假了再过去？</t>
+  </si>
+  <si>
+    <t>这样的家长，放假再规划就比较匆忙，选择的辅导班和学习方式不一定适合孩子。再说刚放假是不是得让孩子放松1天？咱现在需要提前规划的，我们提前分析一下孩子学习的习惯和哪些关键知识欠缺，给孩子规划一下这个暑假如何让他针对性地来补习，实现提成绩有效学习。案例影响：他们年级谁谁，上个周末已经过来了解过了，试完课孩子觉得老师讲的基本能听懂，听不懂还能听第二遍，说真好。你这个周六带孩子过来试试，过几天人更多，到时候我们担心照顾不过来，孩子问题再分析得不透。</t>
+  </si>
+  <si>
+    <t>阶段</t>
+  </si>
+  <si>
+    <t>复习前置知识的重要性</t>
+  </si>
+  <si>
+    <t>当下学习知识点的重要性</t>
+  </si>
+  <si>
+    <t>期中考前</t>
+  </si>
+  <si>
+    <t>期中考前学的相交线与平行线，很多孩子一遇到综合图就抓瞎，如遇到‘拐角模型’完全不知道怎么做辅助线，或者推理过程写得像写小作文一样不规范，总是被扣过程分。这块学不好，主要是因为初一上学期‘线段与角’的几何基础没打牢，缺乏几何直观和基本的逻辑书写训练。建议先补习上学期的几何基础概念和规范书写，不然后面复杂的几何证明题孩子连第一步都迈不出去。</t>
+  </si>
+  <si>
+    <t>期中考前要学的平行线性质与判定是整个初中几何证明的‘敲门砖’，在中考里几何证明题占分极重，这块要是学不透，对后续初二的全等三角形、初三的圆的学习影响很大，会导致中考几何大题直接丢掉十几分，所以一定要注重同步学习。期中考的难点是几何推理的严密逻辑和实数的混合运算，一定要趁现在赶紧攻克，帮孩子建立几何自信！</t>
+  </si>
+  <si>
+    <t>期末考前</t>
+  </si>
+  <si>
+    <t>期末考前学的二元一次方程组和不等式组，很多孩子一碰到应用题就发懵，如遇到行程问题、利润问题根本读不懂题意，列不出式子，或者算着算着就出错了。这块学不好，主要是因为初一上学期的‘一元一次方程’解法不够熟练，找等量关系的能力没练出来。建议先补习上学期的方程解题思路和计算基本功，基础不牢，后面的复杂方程根本解不对。</t>
+  </si>
+  <si>
+    <t>期末考前要学的方程组和不等式的应用是中考必定会考的拿分点，中考地位极高，应用题加计算经常占到 15-20 分，对后续初二的一次函数、初三的二次函数解析式求解的学习影响很大，因为学函数必须要有极强的解方程能力。所以一定要注重同步学习；期末考的难点是列方程解实际应用题，这一关必须跨过去，直接关系到孩子初二数学能不能稳住！</t>
+  </si>
+  <si>
+    <t>2.初一英语</t>
+  </si>
+  <si>
+    <t>期中考前学的特殊疑问词、名词复数、祈使句、情态动词（can/have to/must），是孩子最容易丢分的地方。比如特殊疑问词分不清用法、名词复数变形错、祈使句否定形式搞混、情态动词后动词原形忘记加。这块学不好，主要是因为初一上的一般现在时、基础句型，建议先补习初一上核心语法和基础句型，把旧知识吃透，新内容才能学明白。</t>
+  </si>
+  <si>
+    <t>期中考前要学的特殊疑问词、名词复数、祈使句、情态动词，是初一下核心语法重难点，在中考中直接占分 8—12 分，对初二完形填空、语法填空、写作的影响非常大，所以一定要注重同步学习。期中考的难点就在于语法点细碎易混淆、题型灵活不会套用，现在不抓牢，后面学名词性物主代词、可数 / 不可数名词时会更吃力，直接影响后续单元和期中、期末总分。</t>
+  </si>
+  <si>
+    <t>期末考前要学的一般过去时，孩子做题时常见时间状语分不清、动词过去式忘写、不规则动词记不住。这块学不好，主要是因为前面的现在进行时、一般现在时时态体系没理清，建议先补习两大基础时态的区别 + 核心不规则动词表，理清时态逻辑。</t>
+  </si>
+  <si>
+    <t>期末考前要学的一般过去时，是初一下语法的“压轴重头戏”，中考语法填空、写作、阅读细节题中占分高达 10—15 分。它是初二所有复杂时态的基础，现在学扎实，期末考能直接拉分，也能为初二学习 “一般过去时 + 过去进行时” 组合扫清障碍，一步不落后，全程不掉队。</t>
+  </si>
+  <si>
+    <t>二、初二</t>
+  </si>
+  <si>
+    <t>1.初二数学</t>
+  </si>
+  <si>
+    <t>期中考前学的二次根式的计算和勾股定理的应用，很多孩子错得一塌糊涂，如根号下的化简总是错，或者遇到综合图形不知道怎么构造直角三角形来解题。这块学不好，主要是因为初二上学期的‘整式乘除’基本功不扎实，以及‘全等三角形’的辅助线没过关。建议先补习上学期的代数变形和全等三角形常见模型，不然现在的计算和几何证明孩子根本无从下手。</t>
+  </si>
+  <si>
+    <t>期中考前要学的勾股定理和平行四边形是初中几何的‘核心大心脏’，中考地位极其关键，各种几何压轴题里必考，占分高达 20-30 分！这对后续初三的相似三角形、圆的学习影响很大，所以一定要注重同步学习。期中考的难点是勾股定理的逆定理应用和四边形性质的灵活转化，初二下学期是两极分化最严重的时候，这时候一旦掉队，后面就真的很难追了！</t>
+  </si>
+  <si>
+    <t>期末考前学的一次函数，是无数初中生的‘噩梦’，很多孩子根本不理解函数图像，如看到题目里的字母 k 和 b 的正负号就发懵，遇到一次函数跟面积结合的题完全没思路。这块学不好，主要是因为初一下学期的‘平面直角坐标系’和‘二元一次方程’没吃透。建议先补习坐标系的基础概念和解方程组，不然连函数的图象在哪个象限都画不出来，更别提做大题了。</t>
+  </si>
+  <si>
+    <t>期末考前要学的一次函数是初中接触的第一个真正意义上的函数，也是代数与几何的第一次深度结合，中考必考大题，占分 15 分以上！这对后续初三反比例函数和二次函数（中考压轴题，占 25 分以上）的学习影响很大，学不好一次函数，初三的二次函数绝对听天书，所以一定要注重同步学习。期末考的难点是数形结合思想的应用和特殊平行四边形的综合证明，这是拉开学霸和普通孩子差距的绝对关键点，趁期末前必须帮孩子拿下！</t>
+  </si>
+  <si>
+    <t>2.初二英语</t>
+  </si>
+  <si>
+    <t>期中考前学的动词不定式作宾语补足语、情态动词表建议、反身代词、连词（although, until, so that），是孩子最容易丢分的重灾区。比如不定式前忘记加 to、情态动词后用错动词形式、反身代词指代混乱、连词逻辑关系搞反。这块学不好，主要是因为初一所学的基础动词用法、情态动词基础、简单句结构没打牢，建议先补习初一核心动词搭配、基础句型和代词用法，把旧知识漏洞补上，新语法才能学明白。</t>
+  </si>
+  <si>
+    <t>期中考前要学的动词不定式、情态动词表建议、反身代词、连词，是初二上核心语法重难点，在中考中直接占分 10—15 分，对初三完形填空、语法填空、写作的逻辑表达影响非常大，所以一定要注重同步学习。期中考的难点就在于语法点交叉出题、句式结构复杂、逻辑关系难判断，现在不抓牢，后面学到形容词和副词特殊用法、大数复习等内容时会更吃力，直接影响后续单元和期中、期末总分。</t>
+  </si>
+  <si>
+    <t>期末考前学的过去进行时、连词（so…that, unless, as soon as）、现在完成时（一）（二），是孩子最容易丢分的地方。比如过去进行时和一般过去时混淆、连词逻辑关系判断不清、现在完成时的时间标志词和延续性动词不会用。这块学不好，主要是因为之前学的一般过去时、现在进行时、基础连词等时态和逻辑基础没打牢，建议先补习初二期中前的核心时态和连词用法，把旧知识体系理清，新语法才能学透。</t>
+  </si>
+  <si>
+    <t>期末考前要学的过去进行时、高级连词、现在完成时，是初二下语法的“压轴重头戏”，在中考中直接占分 15—20 分，是初三学习复杂时态、长难句写作的核心基础。现在不学扎实，不仅会直接拉低期末考总分，还会导致初三学习被动语态、宾语从句时完全跟不上，影响整个中考英语的分数上限，所以必须现在同步学稳、学透。</t>
+  </si>
+  <si>
+    <t>3.初二物理</t>
+  </si>
+  <si>
+    <t>初二上核心为机械运动、光现象、质量与密度，是初中物理的入门基础。下学期将学习力、运动和力、压强、浮力，全部依赖上学期的单位换算、公式规范、实验思维、简单计算逻辑。很多同学一学到压强、浮力就不会做题，本质是受力分析不会、公式乱用、单位换算混乱。上学期基础模糊，会直接导致下学期力学听不懂、题不会解，成绩快速下滑。及时复习可巩固入门基础，降低力学衔接难度，避免知识断层，为力学学习筑牢根基。</t>
+  </si>
+  <si>
+    <t>初二下前半学期为力、运动和力、压强、浮力，是初中物理力学核心板块，也是中考分值最高、难度最大的内容之一。它承接初二上入门知识，正式进入系统力学，是物理成绩最容易分化的关键节点。压强、浮力在中考中分值高、常出大题，既是期中考试重点，也是后续学习功、机械能、简单机械的必备基础，直接决定期中考试成绩，更影响整个初中物理的分数上限，必须同步学扎实。</t>
+  </si>
+  <si>
+    <t>初二下期中前核心为力、运动和力、压强、浮力，是学习功和机械能、简单机械的直接前提。浮力依赖压强与受力分析，功、功率、机械效率必须用到力与运动的知识。很多同学到期末不会做综合题，主要是力、压强、浮力没吃透，受力分析、公式应用不熟练。复习前面内容，能打通力学逻辑链条，避免解题思路断裂，保证期末大题能上手、能得分。</t>
+  </si>
+  <si>
+    <t>初二下后半学期为功和机械能、简单机械（杠杆、滑轮、机械效率），是初二力学的压轴收尾内容，高度依赖前半学期力、压强、浮力知识。这部分是期末必考压轴题，也是中考力学综合题的核心载体，分值大、拉分明显，直接决定期末成绩高低，同时为初三总复习打下关键基础。学好它，才能完整构建力学体系，保证中考物理稳定高分。</t>
+  </si>
+  <si>
+    <t>四、高一</t>
+  </si>
+  <si>
+    <t>1.高一数学</t>
+  </si>
+  <si>
+    <t>期中考前要学平面向量和解三角形。很多同学一开始学向量就被各种运算绕晕了，比如向量加法搞不清方向，数量积的公式记反，算着算着符号就错了；解三角形的时候，题目给个条件，不知道用正弦定理还是余弦定理，边角互化经常搞混，最后算出来的角度也不在范围内。这块学不好，主要是因为高一上学期学的三角函数没吃透，三角函数的图象、诱导公式、恒等变换都模模糊糊，解三角形里全是这些内容。建议先把必修第一册的三角函数重新复习一遍，特别是三角函数的定义、同角关系、两角和差公式，把这些理清了，解三角形才能算对。</t>
+  </si>
+  <si>
+    <t>期中考前要学的平面向量和解三角形，是高中数学从代数跨向几何应用的桥梁。向量不仅是高一下学期的重点，更是高二空间向量的基础，如果现在向量的坐标运算和几何意义没搞懂，后面立体几何用向量法解题就彻底懵了。这部分在高考里直接考查约 15-20 分，经常以小题出现，解三角形还容易出大题。比如解三角形中的最值问题，综合了函数和不等式，是很多同学的丢分点。所以一定要注重同步学习，把向量的运算练熟，把正余弦定理的适用条件记清。</t>
+  </si>
+  <si>
+    <t>期末考前要学立体几何初步和统计与概率。很多同学看到立体几何的证明题就头疼，比如证明线面平行，明明条件都给了，就是不知道怎么写步骤，或者逻辑跳步被扣分；概率题里，事件的关系总是理不清，古典概型数个数经常数错。这块学不好，主要是因为初中平面几何基础弱，空间想象能力没培养起来，高一上学期的逻辑用语和推理证明也没练到位。建议把必修第一册的常用逻辑用语翻出来看看，再找些初中几何题练练手，把“因为、所以” 的逻辑链条理顺了，立体几何的证明才能严谨。</t>
+  </si>
+  <si>
+    <t>期末考前要学的立体几何和统计概率，是高考的两大固定板块。立体几何每年必考一道大题加若干小题，加起来 22 分左右，而且高二还要用空间向量再学一遍立体几何，如果现在线面位置关系的判定定理没掌握，高二的建系法就成了无源之水。统计概率高考占 17-22 分，题目越来越灵活，常与生活情境结合，比如抽样方法、频率分布直方图，现在不把基本概念搞懂，高三综合复习时根本跟不上。期末考的难点比如立体几何的动点轨迹问题、概率中的条件概率，都需要现在打好基础。</t>
+  </si>
+  <si>
+    <t>2.高一化学</t>
+  </si>
+  <si>
+    <t>期中考前要学硫 / 氮及其化合物、化学反应与能量。很多同学一开始学硫 / 氮化合物就被复杂的转化关系绕晕了，比如二氧化硫的氧化性与还原性分不清，浓硝酸和稀硝酸的反应产物记混，写方程式时经常漏写条件、配平出错；学习化学反应与能量时，对化学键与能量变化的关系理解模糊。这块学不好，主要是因为高一上学期学的物质的量、氧化还原反应没吃透，硫氮化合物的反应大多是氧化还原反应，能量计算也离不开物质的量的相关公式。建议先把必修第一册的物质的量、氧化还原反应重新复习一遍，特别是物质的量浓度计算、得失电子守恒配平，把这些理清了，硫氮化合物的方程式书写和能量计算才能算对。</t>
+  </si>
+  <si>
+    <t>期中考前要学的硫 / 氮及其化合物、化学反应与能量，是高中化学元素化合物知识和能量变化板块的核心，是连接高一上学期基础化学与高二化学深化学习的桥梁。硫 / 氮及其化合物既是高中化学的重点，也是高考的高频考点，而化学反应与能量则是后续学习化学反应速率、化学平衡及原电池的基础，如果现在焓变的计算、吸热放热反应的判断没搞懂，后面学习化学平衡中的能量变化、原电池的能量转化就会寸步难行。这部分在高考里直接考查约 15-20 分，经常以选择题、填空题出现，硫 / 氮化合物的推断题、能量计算大题也是常见丢分点。所以一定要注重同步学习，把硫 / 氮化合物的转化关系、相关反应记熟，把能量计算的公式和思路理清。</t>
+  </si>
+  <si>
+    <t>期末考前要学化学反应速率、原电池、有机化学等。很多同学面对化学反应速率的计算就头疼，对影响速率的因素理解不透彻，不能结合题干条件分析速率变化的原因；原电池的正负极判断、电极反应式书写经常出错，分不清电子流向和离子移动方向；有机化学中，官能团的性质记混，同分异构体的书写漏写或重复，不能根据官能团判断反应类型。这块学不好，主要是因为高一上学期学的化学键、物质结构基础薄弱，氧化还原反应的本质掌握不扎实。建议把必修第一册的化学键、氧化还原反应再系统复习一遍，理顺物质结构与性质的关联，把基础知识点吃透，才能顺利掌握期末考前的重点内容。</t>
+  </si>
+  <si>
+    <t>期末考前要学的化学反应速率、原电池、有机化学，是高考化学的三大核心板块，分值占比高、考查形式灵活。化学反应速率和原电池是化学原理的核心内容，每年高考必考，加起来约 18-23 分，既有小题考查基础知识点，也有大题结合化学平衡、工业生产情境考查综合应用，而且高二还要深入学习化学平衡，若现阶段没掌握，高二的学习会举步维艰。有机化学是高中化学的重点难点，高考占 20-25 分，也是高二深入学习的基础；化学与资源（海水、金属）则是高考情境题的高频载体，经常结合工业生产流程考查物质制备、提纯，占分约 8-12 分。期末考的难点比如化学反应速率的图像分析、原电池的复杂电极反应式书写、有机同分异构体的判断等，都需要现在打好基础，为后续学习和高考复习筑牢根基。</t>
+  </si>
+  <si>
+    <t>3.高一英语</t>
+  </si>
+  <si>
+    <t>期中考前学的被动语态、情态动词以及长难句初探，很多同学一遇到长句子就发懵，全靠单词拼凑猜意思。比如很多同学一做题就崩溃。比如做完形填空，单看选项单词都认识，连到句子里就选错，全靠语感瞎蒙；在写作文时，想表达“这个问题已经被解决了”，经常漏掉 be 动词写成主动语态；做阅读时找不准主干，导致理解偏差。这块学不好，主要是因为高一上学期学的高一上学期的核心词汇（特别是词根词缀）和五大基本句型和基础时态没吃透，连主语、谓语、宾语都划分不清楚，基本时态的构成也模棱两可。建议先补习上学期的句子成分划分和一般现在、一般过去等基础时态，把句子的 “地基” 打牢了，现在的语法和长难句才能看懂。</t>
+  </si>
+  <si>
+    <t>期中考前要学的被动语态、情态动词及长难句分析，是高中英语从“词法” 跨向 “句法” 应用的桥梁。长难句解析不仅是高一下学期的重点，更是整个高中阅读理解的基础。在高考里，阅读理解和完形填空占了极大比重，如果现在阅读速度提不上来、长难句看不懂，对后续的 阅读速度和准确率影响很大，很多孩子高二高三英语考试根本做不完卷子。所以一定要注重同步学习，把长难句的主干提取能力培养起来。</t>
+  </si>
+  <si>
+    <t>期末考前学的被动语态、名词性从句（宾语从句、主语从句等）和词汇深度拓展，是很多同学的“重灾区”。比如做语法填空选引导词，到底用 that、what 还是 which，很多孩子全靠语感瞎蒙，一做就错；阅读遇到长句子套小句子，逻辑完全理不清。这块学不好，主要是因为初中和高一上的词性概念（如及物动词与不及物动词）没搞懂，且上学期的定语从句基础薄弱，混淆了不同从句的功能。建议先往前复习词性分类和定语从句的基础概念，把前面的语法脉络理顺，名词性从句才能学明白。</t>
+  </si>
+  <si>
+    <t>期末考前要学的名词性从句和应用文高级句式，是整个高中书面表达的核心骨架。它不仅是单句语法的难点，更是高考书面表达拿高分的关键。在高考里，语法填空必考从句，而在作文中写出一个漂亮的主语从句或同位语从句，能让阅卷老师眼前一亮，单篇作文直接提档 2-3 分。这部分词汇和语法的深度，对后续比较难的 “非谓语动词” 的学习影响很大，所以一定要注重同步学习，把名词性从句的引导词用法彻底记清。</t>
+  </si>
+  <si>
+    <t>4.高一物理</t>
+  </si>
+  <si>
+    <t>高一上核心为运动的描述、匀变速直线运动、相互作用、牛顿运动定律，是整个高中物理的基石。下学期将学习曲线运动、万有引力、机械能守恒，均以上学期知识为基础。牛顿定律是分析平抛、圆周运动的核心工具，受力分析贯穿所有动力学问题，运动学公式是解题必备基础。上学期概念模糊会直接导致下学期听不懂、不会解题。同时上学期是物理思维建立的关键阶段，扎实掌握能降低衔接难度，避免知识断层，为后续复杂模型分析筑牢根基。</t>
+  </si>
+  <si>
+    <t>高一下前两章为曲线运动、万有引力与航天，是力学核心进阶内容。它承接高一上的直线运动、受力分析与牛顿定律，首次将力学拓展到平抛、圆周等复杂模型，是思维转型的关键节点。圆周运动的向心力、运动的合成与分解，既是期中必考主干知识，也是后续机械能、动量综合题的必备工具；万有引力则是高考高频考点，模型典型、公式密集。学好这两章能稳固力学体系，避免知识断层，直接决定期中考试成绩，也为后半学期及整个高中物理打下决定性基础。</t>
+  </si>
+  <si>
+    <t>高一下期中前核心为曲线运动、万有引力与航天，是衔接力学与天体、能量问题的关键。期末将学习机械能守恒定律、动量定理，二者联系极为紧密。曲线运动的分解方法、向心力公式，是机械能、动量综合题的必备基础；万有引力中的圆周运动模型，常与动能定理结合考查。这部分内容思维难度大、公式多，若遗忘薄弱，会直接导致期末综合大题无从下手。及时复习可巩固模型与方法，打通力学知识体系，避免期末复习时出现知识断层，保证综合题解题思路完整。</t>
+  </si>
+  <si>
+    <t>高一下后两章为机械能守恒定律、动量定理，是高中力学的核心收尾内容。这两章高度依赖前半学期曲线运动、受力分析等知识，同时综合了高一全年的物理方法。机械能、动量是期末必考压轴题型，也是高考力学综合题的核心载体。它们不仅能解决复杂动力学问题，更是连接力学与电磁学的关键桥梁。掌握好这部分内容，能完整构建高一力学知识体系，直接决定期末成绩上限，同时为高二物理学习筑牢重要基础。</t>
+  </si>
+  <si>
+    <t>四、高二</t>
+  </si>
+  <si>
+    <t>1.高二数学</t>
+  </si>
+  <si>
+    <t>期中考前要学计数原理和随机变量及其分布。很多同学做排列组合题时，总是分不清“选人” 和 “排序”，比如 “从 5 个人中选 3 个人去参加 3 项不同的活动” 和 “从 5 个人中选 3 个人组成一组”，到底乘不乘顺序，一错就是全错；还有分布列的期望方差，公式背了又忘，算着算着就乱了。这块学不好，主要是因为高一学的统计概率基础没打牢，比如古典概型的计数方法、互斥事件和独立事件的区分。建议先把必修第二册的概率初步复习一遍，把最基本的事件关系和概率公式重新捋一捋，再回头学排列组合才能理解为什么这么算。</t>
+  </si>
+  <si>
+    <t>期考前要学的计数原理和随机变量分布，是高考中区分度比较大的部分，常以实际情境出现，比如体育比赛、抽奖、产品质量检验等，分值约 17-22 分。这部分内容不仅考计算，更考阅读理解能力，比如题目里说 “不放回抽取” 和 “有放回抽取”，对应的分布完全不同。期中考的难点比如超几何分布和二项分布的识别，很多同学看到题目分不清用哪个，导致全题覆没。如果现在不把这些模型吃透，后面高三刷题时你永远在碰运气。所以一定要同步学习，多练情境题，把分布列的计算步骤规范起来。</t>
+  </si>
+  <si>
+    <t>期末考前要学成对数据的统计分析和导数的综合应用。导数压轴题是很多学生的噩梦，比如给一个含参数的函数，让你证明不等式恒成立，很多同学求完导数就不知道接下来该讨论什么，分类讨论不是漏情况就是分得太碎；还有统计里的回归分析，公式复杂，套用经常出错。这块学不好，主要是因为高二上学期的导数基本运算不熟练，比如复合函数求导、导数的几何意义没搞透，高一函数的性质也没掌握扎实。建议先把选择性必修第二册的导数概念和基本公式重新复习一遍，再把必修第一册的指数对数函数捡起来，把函数的图象和单调性记熟，这样面对导数大题才有思路。</t>
+  </si>
+  <si>
+    <t>期末考前要学的导数综合应用和统计案例分析，是高考数学的“压舱石”。导数大题基本固定在最后两道，12-17 分，专门用来拉开分数差距，比如零点问题、恒成立求参数范围、隐零点代换，每一个专题都需要扎实的函数功底和灵活的分类讨论思想。统计综合近年也开始出现在大题中，结合概率和期望，总分值加起来接近 30 分。可以说，这半个学期的内容直接决定了你高考能上 120 还是 140。期末考的难点比如导数中的极值点偏移、统计中的非线性回归，都是需要反复琢磨的题型。现在必须一步一个脚印，每道错题都抠透，别指望高三再来补，因为高三一轮复习节奏快，根本没时间给你慢慢消化这些压轴题。</t>
+  </si>
+  <si>
+    <t>2.高二化学</t>
+  </si>
+  <si>
+    <t>期中考前要学选择性必修 2（物质结构与性质）。很多同学一开始学物质结构与性质就被复杂的原子结构、规律绕晕了，比如电子排布式与轨道表示式分不清，杂化轨道类型与分子空间构型记混；学习元素周期律应用时，对原子结构与元素性质的关联理解模糊。这块学不好，主要是因为高一学的物质结构、化学键没吃透，物质结构与性质的核心知识点都是高一物质结构的延伸，原子结构、化学键的基础直接影响电子排布、晶体结构的判断。建议先把必修第一册的物质结构、化学键重新复习一遍，特别是原子结构示意图、化学键类型判断、元素周期律基础，把这些理清了，物质结构与性质的相关判断和分析才能做对。</t>
+  </si>
+  <si>
+    <t>期中考前要学的选择性必修 2（物质结构与性质）全部内容，是高中化学物质结构板块的核心，是连接高一物质结构基础与高二化学深化学习的桥梁。选择性必修 2（物质结构与性质）既是高中化学的重点，也是高考的高频考点。如果现在原子结构、杂化轨道、化学键、晶体基础的相关判断没搞懂，后面学习晶体分析的晶胞计算、有机化合物的空间构型推断就会寸步难行。这部分在高考里直接考查约 12-18 分，经常以选择题、填空题出现，原子结构推断题、化学键与物质性质判断题、晶体基础判断题也是常见丢分点。所以一定要注重同步学习，把原子结构、杂化轨道类型、化学键的判断方法、晶体基础知识点记熟，把物质结构与元素性质、晶体性质的关联理清。</t>
+  </si>
+  <si>
+    <t>期末考前要学选择性必修 2（物质结构与性质）、选择性必修 3（有机化学基础）所有内容。很多同学面对选必 2 晶体分析就头疼，晶体类型判断，晶胞中微粒个数计算、晶体堆积方式判断经常出错；选必 3 有机化学中，同分异构体（尤其是多官能团同分异构体）的书写漏写或重复，不能根据官能团推断有机物的反应类型、推导有机物结构，有机合成路线设计无从下手。这块学不好，主要是因为高一有机化学基础薄弱，高一有机基础是选必 3 有机化学学习的核心前提。建议把高一所学的有机化学基础内容重点复习一遍，夯实高一有机核心知识点，把基础吃透，才能顺利掌握期末考前难点内容。</t>
+  </si>
+  <si>
+    <t>期末考前要学的选择性必修 2（物质结构与性质）、选择性必修 3（有机化学基础），是高考化学的两大核心板块，分值占比高、考查形式灵活。晶体分析是物质结构板块的难点内容，每年高考必考，约占 10-15 分，既有小题考查晶体类型判断、晶胞微粒计算，也有大题结合物质结构情境考查综合应用，而且晶体结构的相关知识还是高考物质结构选做题的核心，若现阶段没掌握，后续高考复习会举步维艰。有机化学基础是高中化学的重点难点，高考占 20-25 分，也是后续有机合成、有机推断大题的学习基础；两者结合更是高考情境题的高频载体，经常结合新材料、新物质情境考查结构推断、性质分析，占分约 5-8 分。期末考的难点比如晶胞结构计算、晶格能大小比较、多官能团同分异构体书写、有机合成路线设计等，都需要现在打好基础，为后续学习和高考复习筑牢根基。</t>
+  </si>
+  <si>
+    <t>3.高二英语</t>
+  </si>
+  <si>
+    <t>期中考前学的非谓语动词（动词 ing、ed 和 to do 形式）以及复杂篇章阅读，这是高中最难的语法，没有之一。比如做语法填空，孩子根本不知道该填主动的 ing 还是被动的 ed，经常张冠李戴；做七选五阅读时，上下文逻辑连词完全找不准。做读后续写，孩子憋了半天只能写出 “He was happy and he smiled”，完全不会用非谓语作伴随状语来丰富细节。这块学不好，主要是高一的句子成分，从句和时态语态没掌握好，找不到动作的发出者（逻辑主语），导致非谓语形式判断失误。建议先补习定语从句和句子主干分析，把前面的句子结构理顺了，非谓语动词才能开窍。</t>
+  </si>
+  <si>
+    <t>期中考前要学的非谓语动词，是高考语法的“天花板”，也是拉开尖子生和普通生差距的关键。在高考里，语法填空必考非谓语（至少占 3-4.5 分），更重要的是，它是高考 “读后续写” 拿高分的秘密武器，不会用非谓语，作文全是小学生一样的简单句，直接掉档。这部分对后续高三的一轮总复习进度影响很大，所以一定要注重同步学习，把非谓语动词的主被动关系和时间先后关系彻底搞懂。</t>
+  </si>
+  <si>
+    <t>期末考前学的特殊句式（虚拟语气、倒装句、强调句），读后续写微技能，说明类复杂文本阅读，很多同学一听公式就头大。比如写“如果我昨天没熬夜就好了”，虚拟语气的时态总是写错；倒装句的助动词语序也经常搞反。这块学不好，主要是因为高一高二的基础时态和状语从句没学扎实，词汇积累不够，导致现在套高级句式的公式都套不对。建议先往前复习高中的基本时态和状语从句引导词，时态过关了，虚拟语气和特殊句式就是纸老虎。</t>
+  </si>
+  <si>
+    <t>期末考前要学的特殊句式（倒装、强调、虚拟）和高阶阅读技巧（主旨大意、推理判断），是高考冲刺高分的“提分神器”。在高考里，无论是阅读的压轴题，还是作文的亮点句，都离不开这些特殊句式。用上一个漂亮的倒装句，能极大地提升文章的语言层次。这部分对后续马上到来的高三各种模拟测的得分上限影响很大，所以一定要注重同步学习。趁着高二期末，把这些高级句式和阅读逻辑彻底吃透，高三才能轻松提分，拉开与别人的差距。</t>
+  </si>
+  <si>
+    <t>4.高二物理</t>
+  </si>
+  <si>
+    <t>高二上主要为电场、恒定电流、磁场，是电磁学核心基础，也是高二下学习电磁感应、交变电流的直接前提。电场力、电势能、安培力、洛伦兹力等分析方法，与电磁感应的受力、能量问题高度关联；电路分析、欧姆定律更是理解交变电流、变压器的必备基础。同时电磁学综合题常串联高二上下全部内容，是期末与高考压轴考点。若上学期知识薄弱，会直接导致电磁感应模型看不懂、综合题不会解。及时复习可巩固电磁学主干框架，衔接新旧知识，避免出现断层，为高二下学期学习与后续备考筑牢关键根基。</t>
+  </si>
+  <si>
+    <t>高二下期中前主要学习电磁感应、交变电流，是电磁学板块的核心进阶内容，承接高二上电场、磁场、恒定电流，也直接衔接后续电磁综合与传感器内容。法拉第电磁感应定律、楞次定律、自感、变压器等知识，综合受力分析、能量守恒、电路规律，既是期中考试重点，也是高考电磁压轴题的核心载体。这部分模型复杂、综合性强，既是对高一力学方法的深化运用，也是电磁学体系的关键一环。学好期中前内容，能顺利完成从“场” 到 “感应” 的思维过渡，避免知识断层，为后半学期学习和综合解题打下坚实基础，直接决定本学期物理成绩。</t>
+  </si>
+  <si>
+    <t>高二下学期期中前核心内容为电磁感应、交变电流，是电磁学的关键进阶部分。这部分知识紧密衔接高二上学期的电场、磁场、电路规律，同时也是期末学习传感器、电磁综合应用的重要基础。楞次定律、法拉第电磁感应定律、感应电路分析，既是期中主干考点，也是期末电磁综合题的核心工具；交变电流与变压器模型，常和电路、能量结合命题。期中前内容公式多、规律抽象，若掌握不牢，会直接导致期末综合题无从下手。复习这部分内容能完善电磁学体系，打通前后知识关联，避免解题思路断裂，对稳定期末成绩、夯实高考电磁学基础至关重要。</t>
+  </si>
+  <si>
+    <t>人教版高二下学期期中后主要学习传感器、电磁学综合应用及近代物理初步，是本学期电磁学收尾与知识升华部分。这部分内容高度依赖期中前的电磁感应、交变电流，也综合高二上电场、磁场、电路规律，是构建完整电磁体系的关键环节。传感器侧重实际应用，常结合电路与感应现象命题；近代物理初步虽偏概念，但也是期末必考内容。学习这部分既能巩固前期核心规律，训练综合解题思路，又是对高中物理主干知识的完善。学好期中后内容，可补齐知识短板，提升综合解题能力，直接影响期末考试成绩，同时为一轮复习和高考打下完整知识基础。</t>
   </si>
   <si>
     <r>
@@ -197,9 +2040,6 @@
 带来体验1个小时就够了，先安排给孩子的学习时间</t>
   </si>
   <si>
-    <t>孩子不愿意学</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -354,9 +2194,6 @@
       </rPr>
       <t>孩子上的辅导班以讲基础为主吗？是针对咱家孩子这个层次的吗？大部分还是要按照中等左右以上设定课程方案，咱长期处在追赶的状态，心态疲惫时间长了成绩不但提不上去，也容易失去兴趣。</t>
     </r>
-  </si>
-  <si>
-    <t>买了之后，孩子不愿意学怎么办？</t>
   </si>
   <si>
     <r>
@@ -432,9 +2269,6 @@
   </si>
   <si>
     <t>孩子比较叛逆，不听劝</t>
-  </si>
-  <si>
-    <t>现在很多孩子都比较叛逆，家长要好好引导，但不是一直唠叨。要坚定你的态度，家长的态度，决定孩子的成绩。孩子吃喝拉撒都靠你，不可能完全不听劝。你带着他出来转转，也不一定要报课，让他来看看，喜不喜欢，我跟他聊聊。</t>
   </si>
   <si>
     <t>已经有了其他的补习方式</t>
@@ -457,12 +2291,6 @@
     <t>和孩子商量商量，担心给孩子买了孩子觉得给自己增加负担？</t>
   </si>
   <si>
-    <t>你给孩子买课，帮他提高，这还商量啥？你得和孩子说：别的家长都舍不得给孩子买课，舍不得花这个钱，妈妈多爱你呢，我直接给你买了。我看你做题做到XX点，这么晚我都心疼，妈妈也帮不了你别的，你用这个课估计很快就写完作业了。你得无条件相信孩子。再说了，孩子在这都说可以、想上了，你还一直追着问，你自己想想多有压力啊。你想听孩子烦躁了说"不学了"啊？那是钱的事情吗？那孩子上学这条路就断了。趁他有兴趣，咱做家长就无条件支持、相信自己孩子才行。</t>
-  </si>
-  <si>
-    <t>这个课和我们考的题不一样</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -490,9 +2318,6 @@
       </rPr>
       <t>，正好解决学习浮于表面，错题不反思总结，一错再错或稍变换题型就不会了的情况</t>
     </r>
-  </si>
-  <si>
-    <t>在学校/辅导班老师看着都不学呢，这网课更不学了</t>
   </si>
   <si>
     <r>
@@ -541,9 +2366,6 @@
       <t xml:space="preserve">，你只要有网随时随地可以了解孩子学习的情况。
 </t>
     </r>
-  </si>
-  <si>
-    <t>放学晚/放假时间少，没时间听这么多课</t>
   </si>
   <si>
     <r>
@@ -640,51 +2462,18 @@
     <t>你们电话哪里来的？</t>
   </si>
   <si>
-    <t>应该是小学在学校门口做宣传时，之前留的。我们是做弱课提升的，主要就是想给孩子提升成绩的。您要有需求联系我哈，要是没有需求，真是抱歉了，打扰您了哈。您也可以记一下我电话，有需求了联系我，我们专门做初高中辅导19年了，在咱当地也是相对最专业的哈。</t>
-  </si>
-  <si>
-    <t>孩子时间紧、累，没有时间学习/作业多，没时间怎么办？</t>
-  </si>
-  <si>
-    <t>主要问题是孩子时间这么紧、这么累，成绩不理想啊。这么辛苦咱们是为了有个好前程吧，不是为了现在上学辛苦以后工作还辛苦。他没有找到适合自己的学习方法，都白白辛苦了。（再分析我们的分层教学及其他孩子使用的案例及我们的按点听课功能）</t>
-  </si>
-  <si>
     <t>时间紧，没时间听，担心给孩子增加负担？</t>
   </si>
   <si>
-    <t>给孩子报名是帮孩子解决问题的，不是增加负担的。有问题了再用，可以很及时地解决问题、做学习补充，没有问题的时候就可以不用啊。（再分析其他孩子使用的案例及我们的按点听课功能）</t>
-  </si>
-  <si>
     <t>课太多听不过来，想报单科怎么办？</t>
   </si>
   <si>
-    <t>新华字典那么多字，一辈子咱也看不过来呀，咱就是得哪里不会听哪里。那还能学校学一遍，来店再学一遍吗？孩子时间也不允许啊。你现在这科（想报的那科）有问题，其他科还等出问题再学吗？就是其他科考满分，以后还有新知识点呢，哪可能没有新学习的需要呢？再说现在单科一年1400/1800元，一年才多少钱（展开算数字），买三科就送全年了，真是没有人买单科的。</t>
-  </si>
-  <si>
     <t>课程这么多，没时间听完，花的钱感觉浪费了？</t>
   </si>
   <si>
-    <t>咱们课程就是个百宝箱/字典，只需要去听课上没听懂的，课上没听懂的都能找到，比想听的找不到好呀。像咱们花二三十万买辆车，也不是天天开，有需要才开呀。比如家里一天做四个菜，也不用全吃呀，选自己想吃的就行，那就很值了。（再分析其他孩子使用的案例及我们的按点听课功能）</t>
-  </si>
-  <si>
     <t>老师讲的和我们学校老师讲的也没啥区别？</t>
   </si>
   <si>
-    <t>跟你们老师讲的差不多，说明我们课程是跟你们学校完全同步的。你看我们的老师都是老师的老师，你们学校的老师都是用我们课程备课。重要的是学校老师讲的你这不是没听懂吗？学校老师不会再给你重复讲了，正好用我们的课程再补充没听懂的，我们的课程可以重复听没听懂的。</t>
-  </si>
-  <si>
-    <t>我们就要找线下1对1/线下的老师？</t>
-  </si>
-  <si>
-    <t>线下1对1效果确实不错，你不能把线下1对1带回家呀，不能随时给你解决问题的。线下一周就1-2个小时解决不了你的问题，你现在的成绩不好就是问题积累了。我们的课程可以每天都用，当天有听不懂的当天拿出10分钟听一下就解决了。</t>
-  </si>
-  <si>
-    <t>考虑线下辅导怎么办？</t>
-  </si>
-  <si>
-    <t>你今天学XX（某学生正在学的知识点）对吗？你要是正好这个知识点有问题，辅导班今天就马上给你讲这个知识点吗？你问题不就是得立刻解决吗？（+前后置知识点展开说）</t>
-  </si>
-  <si>
     <t>孩子认可网课模式想学，但家长不支持？</t>
   </si>
   <si>
@@ -694,21 +2483,12 @@
     <t>家长就想报单科，说没时间听？</t>
   </si>
   <si>
-    <t>初一就有7科，每天都有听不懂的情况。我们这个课程在平时（周一到周五）就像一本会说话的字典，孩子哪里不会就听哪里，不是每个科目都是学生全部去学，而是查缺补漏。这个课程不是说买回去后天天让孩子学、每天都要让孩子学多长时间，就是有事的时候、遇到问题的时候，我们有这个课程能帮学生解决问题，并不是给你增加任务。（然后给家长看其他同年级学生的听课报告）</t>
-  </si>
-  <si>
     <t>这个课和我们考的题不一样？</t>
   </si>
   <si>
-    <t>任何一次考试都和你平时不一样。来我们这学习不是做哪个题的，也不是学哪一科的，是感受我们这边老师的上课方式，能不能帮到你。主要是学学习方法，那么多题永远也做不完，学的是我们这边老师的上课理念和流程及拓宽思维。</t>
-  </si>
-  <si>
     <t>家长强烈要求保证效果/来这里报名能保证提成绩吗？</t>
   </si>
   <si>
-    <t>不需要正面回答，家长可以反问：咱孩子是不是成绩已经落下了？刚了解完咱们的课程，家长你是不是也感觉到了课程很适合孩子？就像您生病了，100%确定这个药对你的症状，如果拿了药您持续服用、正确服用，肯定能治好；如果拿回去后您嫌苦不吃，肯定治不好。所以，我们和您一起鼓励孩子，正确持续地使用，一定能提升。</t>
-  </si>
-  <si>
     <t>家长要求保障效果？</t>
   </si>
   <si>
@@ -718,15 +2498,9 @@
     <t>家长说孩子觉得贵（一些懂事的孩子）？</t>
   </si>
   <si>
-    <t>教育是投资不是消费。孩子要是考的分数高，那是省多少学费啊！民办大学、公立大学学费差出去几万块钱。（本地大家普遍知道的大学）学费才XX钱，你看咱XX私立大学学费要XX呢。孩子是真懂事，但是要想真的孝顺父母，不就是得咱好好学，后期去好大学才能找好工作、多赚钱吗？这个事情咱家长得给孩子定啊，这么懂事的孩子别耽误了。</t>
-  </si>
-  <si>
     <t>已经报辅导班了！</t>
   </si>
   <si>
-    <t>（不要直接挂电话，这些客户都是重视教育的，当下不报后续也有可能报，多跟家长聊聊）孩子报的哪个机构？报的哪几科？一个班几个孩子？（了解辅导班形式、结束时间、报的科目、开学是否走读等，方便后续跟进以及跟其他家长对比）高中不比初中，副科难度也挺大的，而且我们孩子后续高一选哪几科也不确定呢，我们可以送几节副课给孩子，对比着学习几天看看效果。您有时间可以带孩子过来试试看。我们这边效果确实很好，去年有一个叫XXX的学生，中考也是刚刚上一中的分数线，暑假在我们这里学的，第一次月考就到班级13名，全校XXX名了。还有一个叫XXX的学生，也是中考分数很一般，暑假在我们这里学得很好，第一次月考就到班级第9名，现在已经稳定班级5、6名的样子，很不错了。如果维持下去的话，考大学就没问题了。现在孩子上高中了，不比初中，不能随便报个班就算。要给孩子找好的老师，我们这边都是名师授课。你像今年的高考数学全国一卷，我们原题压中了105分，其他科目也压中很多题，语文作文、英语作文都是原题压中的。（这样的客户可能暂时拿不下，或者邀约到店难度大，要了解辅导班结束时间，结束前留意再跟进）</t>
-  </si>
-  <si>
     <t>同学们有报线下班，孩子也想报线下辅导班，如何对比？</t>
   </si>
   <si>
@@ -787,6 +2561,192 @@
       </rPr>
       <t>：辅导班22天，22天后在家刷手机？找同学玩？心又散了。我们的课程，孩子可以预习到军训。虽然不能让孩子太累，每天学习3-4小时休息3-4小时，不至于心散了。</t>
     </r>
+  </si>
+  <si>
+    <t>问题</t>
+  </si>
+  <si>
+    <t>答案</t>
+  </si>
+  <si>
+    <t>简单科技是哪一年创办的？获得了哪些荣誉？</t>
+  </si>
+  <si>
+    <t>简单科技创办于2007年，连续多年获评国家高新技术企业、软件企业。</t>
+  </si>
+  <si>
+    <t>简单科技与北京大学共同开发了什么专利技术？专利号是什么？</t>
+  </si>
+  <si>
+    <t>与北京大学共同开发了"CAT智能引领互动"国家专利技术。专利号：ZL 2007 1 0099746.2，专利种类：发明专利。</t>
+  </si>
+  <si>
+    <t>简单科技目前的基本情况如何？（注册用户、状元人数、服务中心数量等）</t>
+  </si>
+  <si>
+    <t>累计注册用户超过3100万；共有351名简单学员获得省市县中高考状元；智慧课堂应用校400多家；拥有覆盖全国大部分省市的800多家服务中心。</t>
+  </si>
+  <si>
+    <t>简单一百的课程资源有哪些特点？</t>
+  </si>
+  <si>
+    <t>积累20万节精品视频资源；覆盖中学9科3级难度；全部由特级教师、人气教师录制；历经70道工序打磨，制作精良，内容生动严谨。</t>
+  </si>
+  <si>
+    <t>简单科技的教学理念和公司使命是什么？</t>
+  </si>
+  <si>
+    <t>教学理念：自主学习力，终身竞争力；公司使命：让学习变简单、教育更均衡。</t>
+  </si>
+  <si>
+    <t>简单一百的教师团队有什么特点？</t>
+  </si>
+  <si>
+    <t>都是有着丰富经验的精英教师，包括特级教师和人气教师。他们曾是学科带头人、骨干教师等，具有多年教学经验，了解学生的困惑，对中高考有深度的把握。</t>
+  </si>
+  <si>
+    <t>简单一百的师资选拔标准是什么？</t>
+  </si>
+  <si>
+    <t>19年坚持每科只请优秀教师录制，严选优秀师资，多为在北京有多年教学经验的精英教师。</t>
+  </si>
+  <si>
+    <t>简单一百教师的资质要求是什么？平均教龄是多少？</t>
+  </si>
+  <si>
+    <t>特级教师、高级教师、学科带头人、骨干教师或人气教师，平均教龄10年以上。</t>
+  </si>
+  <si>
+    <t>简单一百教师的教学方法是什么？</t>
+  </si>
+  <si>
+    <t>抓住学科本质，培养学科素养，贴近中高考，重视融会贯通，讲1题通1类。</t>
+  </si>
+  <si>
+    <t>简单一百教师的共同特点有哪些？（请列举三点）</t>
+  </si>
+  <si>
+    <t>①高考命题研究专家、全国知名特级教师、教材编者、高考试卷组评价组长/成员，深谙中高考命题方向与特点；②拥有多年线下教学经验，平均10年以上教学经验，直击学生学习难点与痛点；③不放大招，但注重思维的启发与引导，学科方法的提炼，规律的总结；④深入浅出，讲清知识脉络，拓展思维、培养学科能力，提升学科素养。</t>
+  </si>
+  <si>
+    <t>简单一百的教师分为哪几类？请简要说明每类特点。</t>
+  </si>
+  <si>
+    <t>第一类：全国特级教师、高考试题研究专家（常年参加中高考命题、阅卷及教材编写，对中高考脉搏把握更准确）；第二类：北京人气老师，讲得透、有激情、很幽默；第三类：清北、985等毕业教师，功底深厚，能深入还能浅出。</t>
+  </si>
+  <si>
+    <t>简单一百课程覆盖的范围有多大？</t>
+  </si>
+  <si>
+    <t>年级：小学五年级到高三，8个年级；学科：10大学科（包含科学）；教材：全国所有教材版本（港澳台沪除外）。</t>
+  </si>
+  <si>
+    <t>简单一百的课程体系分为哪两大体系？</t>
+  </si>
+  <si>
+    <t>同步教材体系和中高考复习体系。</t>
+  </si>
+  <si>
+    <t>简单一百的课型分为哪几个阶段？每个阶段的学习重点是什么？</t>
+  </si>
+  <si>
+    <t>①春秋跟学校同步学：3层次课程（教材同步、常考提高、满分冲刺），单元复习、期中期末串讲助力复习和考前冲刺；②寒暑假预习：学新知、练好题、明方法，自信应对新学期；③中高考课程：同步学校复习，全面夯基础、攻专题、练应试。</t>
+  </si>
+  <si>
+    <t>简单一百中高考课程是如何划分的？</t>
+  </si>
+  <si>
+    <t>中考：分为一轮、二轮、三轮冲刺课程；高考：分为一轮、二轮和三轮冲刺课程。</t>
+  </si>
+  <si>
+    <t>简单一百课程制作的"70道工序"包括哪些环节？（请列举主要环节）</t>
+  </si>
+  <si>
+    <t>①多重教研：研课标、研教材教辅教参、研考题、研教法、研学情；②课程设计：理知识点题型清单、三层次课程整体设计；③教案打磨：教研和主讲精英教师共同设计教案，特级教师评审；④课程录制：录课前理逻辑、说课，现场学生互动、教研质量把控；⑤反复评课：同学科评、跨学科评、一线教师评；⑥剪辑优化：目录式切课、保留讲课精华部分、添加动画；⑦多轮检课：教研、质检多轮检课，保质保优。</t>
+  </si>
+  <si>
+    <t>简单一百课程的设计理念是什么？</t>
+  </si>
+  <si>
+    <t>老师好、方法优、互动多、品质精；每分钟都有收获，吸引力与收获感兼顾。</t>
+  </si>
+  <si>
+    <t>请简述简单一百"五步学习法"的具体内容。</t>
+  </si>
+  <si>
+    <t>①先练：先做例题，大部分题目系统马上判对错；②后听：老师重启发，每3-5分钟一次互动，在要点处设问，关键思路有要点提醒，每道题有好方法总结；③反思：听完题后及时提醒学生总结反思；④再练：听过讲解后做同类题练习，验证学习效果；⑤追错：错题自动分类汇总，持续追踪。</t>
+  </si>
+  <si>
+    <t>简单乐的四大特点是什么？</t>
+  </si>
+  <si>
+    <t>①同步记忆：教材同步，中高考总复习同步；②题中记忆：10科基础小题逐一过关，语文英语真题句中记；③滚动清错：个性化基础知识错题及时清、集中清；精英教师视频讲错点，真掌握；④短时高效：有效利用零碎时间，用时少，效率高。</t>
+  </si>
+  <si>
+    <t>简单乐覆盖哪10大学科？请列举出来。</t>
+  </si>
+  <si>
+    <t>英语、语文、数学、物理、化学、生物、地理、科学、历史、政治。</t>
+  </si>
+  <si>
+    <t>简单乐的英语学科有什么特点？</t>
+  </si>
+  <si>
+    <t>精选中高考真题，挖空填单词，真人领读，意群记忆，单词会写更会用；闪记模式更能高效记。</t>
+  </si>
+  <si>
+    <t>简单乐的语文学科覆盖哪些内容？</t>
+  </si>
+  <si>
+    <t>覆盖高考300个文言文实词、18个虚词；中考150个实词、15个虚词；涵盖中高考要求背诵的古诗文；囊括中考要求掌握的重点字词。</t>
+  </si>
+  <si>
+    <t>简单乐的数学物理学科有什么特点？</t>
+  </si>
+  <si>
+    <t>滚动记公式、定理、概念、性质，多角度辨析，关键步骤练习，记得准，做题快。</t>
+  </si>
+  <si>
+    <t>英语5维提升方案包含哪五个维度？</t>
+  </si>
+  <si>
+    <t>①AI互动精品课名师精讲：全学段全版本，基础同步、中高考复习，内容全；②练常考题：3种方式练，聚焦考点、精炼好题刷题训练更高效；③背单词：3种方法背、4个难度测、熟悉度标记，记忆曲线助力；④按专项学：语法、阅读、听力等专项细分6-7个level，个性化补弱提强；⑤课文跟读：教材内容全匹配，3种训练进阶提升，逐句跟读，实时评分。</t>
+  </si>
+  <si>
+    <t>英语5维提升方案中"按专项学"是如何细分的？</t>
+  </si>
+  <si>
+    <t>语法、阅读、听力等专项细分6-7个level，个性化补弱提强。</t>
+  </si>
+  <si>
+    <t>什么是数理化351精准提升方案？"351"分别代表什么？</t>
+  </si>
+  <si>
+    <t>数理化351精准提升方案是行业首创的精准提升方案。3：3级难度，学对内容；5：5步学习法，确保学会；1：1对1定制学，坚持学。</t>
+  </si>
+  <si>
+    <t>数理化351方案中"3级难度"是如何划分的？</t>
+  </si>
+  <si>
+    <t>课程分为基础、提高、满分三个难度层次，无论哪个成绩段的学生都能找到适合的课程。</t>
+  </si>
+  <si>
+    <t>数理化351方案中"5步学习法"的具体内容是什么？</t>
+  </si>
+  <si>
+    <t>独创五步互动学习法：先做题，再带着问题听课，听课后反思总结，接着做同类题检测效果，最后追踪错题。全程闭环，保证学习效果。</t>
+  </si>
+  <si>
+    <t>数理化351方案中"1对1定制学"有什么优势？</t>
+  </si>
+  <si>
+    <t>一人一方案，学、记、测三维闭环。老师根据学生情况1v1定制课程，帮助学生个性化学习，破解半途而废。</t>
+  </si>
+  <si>
+    <t>什么是"SAC简单好方法"？S、A、C分别代表什么？</t>
+  </si>
+  <si>
+    <t>SAC简单好方法是通过拆解、抽象、转化三步，不教死记硬背的"大招"，只教举一反三的真方法，做一道题，会一类题。S：拆解；A：抽象；C：转化。</t>
   </si>
 </sst>
 </file>
@@ -799,20 +2759,24 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="43">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="12"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -833,14 +2797,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -855,153 +2814,39 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <sz val="14"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <sz val="10"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <name val="ui-sans-serif"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="ui-sans-serif"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="ui-sans-serif"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="SimSun"/>
+      <sz val="10"/>
+      <name val="ui-sans-serif"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1012,10 +2857,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1030,13 +2874,196 @@
       <name val="SimSun"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFDE3C36"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBA84"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1225,7 +3252,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1255,6 +3282,19 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -1263,14 +3303,53 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFCBCDD1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFCBCDD1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBCDD1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBCDD1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCBCDD1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBCDD1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBCDD1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBCDD1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBCDD1"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFCBCDD1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCBCDD1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCBCDD1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1374,160 +3453,163 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="52">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1535,31 +3617,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1568,8 +3650,113 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1847,9 +4034,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1863,42 +4050,42 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="等线 Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -1924,16 +4111,16 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="等线"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="游明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -1959,40 +4146,66 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2006,38 +4219,20 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
@@ -2096,280 +4291,1395 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="15.2" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="14.7115384615385" customWidth="1"/>
+    <col min="3" max="3" width="24.9519230769231" customWidth="1"/>
+    <col min="4" max="4" width="44.9134615384615" customWidth="1"/>
+    <col min="5" max="6" width="49.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" spans="1:6">
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="135" customHeight="1" spans="1:6">
+      <c r="A2" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" ht="387" spans="1:6">
+      <c r="A3" s="32"/>
+      <c r="B3" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" ht="409.5" spans="1:6">
+      <c r="A4" s="32"/>
+      <c r="B4" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="38.25" customHeight="1" spans="1:6">
+      <c r="A5" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" ht="38.25" customHeight="1" spans="1:6">
+      <c r="A6" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" ht="38.25" customHeight="1" spans="1:6">
+      <c r="A7" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="51.75" customHeight="1" spans="1:6">
+      <c r="A8" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:6">
+      <c r="A9" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" ht="303" spans="1:6">
+      <c r="A10" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="40"/>
+    </row>
+    <row r="11" ht="45" customHeight="1" spans="1:6">
+      <c r="A11" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="42"/>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:6">
+      <c r="A12" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="42"/>
+    </row>
+    <row r="13" ht="45" customHeight="1" spans="1:6">
+      <c r="A13" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="42"/>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:6">
+      <c r="A14" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="42"/>
+    </row>
+    <row r="15" ht="60" customHeight="1" spans="1:6">
+      <c r="A15" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="42"/>
+    </row>
+    <row r="16" ht="60" customHeight="1" spans="1:6">
+      <c r="A16" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="42"/>
+    </row>
+    <row r="17" ht="396" spans="1:6">
+      <c r="A17" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="40"/>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:6">
+      <c r="A18" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="42"/>
+    </row>
+    <row r="19" ht="60" customHeight="1" spans="1:6">
+      <c r="A19" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" s="42"/>
+    </row>
+    <row r="20" ht="60" customHeight="1" spans="1:6">
+      <c r="A20" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="42"/>
+    </row>
+    <row r="21" ht="252" spans="1:6">
+      <c r="A21" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="40"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="1:6">
+      <c r="A22" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="F22" s="42"/>
+    </row>
+    <row r="23" ht="60" customHeight="1" spans="1:6">
+      <c r="A23" s="43" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" s="42"/>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:6">
+      <c r="A24" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" s="42"/>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:6">
+      <c r="A25" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="42"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="1:6">
+      <c r="A26" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="42"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="1:6">
+      <c r="A27" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" s="42"/>
+    </row>
+    <row r="28" ht="25.5" customHeight="1" spans="1:6">
+      <c r="A28" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="50"/>
+    </row>
+    <row r="29" ht="409.5" spans="1:6">
+      <c r="A29" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" ht="409.5" spans="1:6">
+      <c r="A30" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="43" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" ht="409.5" spans="1:6">
+      <c r="A31" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="48" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" ht="409.5" spans="1:6">
+      <c r="A32" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="51" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="D5:D9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="节点常见问题"/>
+  <dimension ref="A1:E57"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="25.8942307692308" customWidth="1"/>
+    <col min="2" max="2" width="141.903846153846" customWidth="1"/>
+    <col min="4" max="5" width="77.6923076923077" style="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:5">
+      <c r="A1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:5">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:5">
+      <c r="C6" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:5">
+      <c r="C7" s="24" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:5">
+      <c r="C8" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:5">
+      <c r="C9" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:5">
+      <c r="C10" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:5">
+      <c r="C11" s="24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:5">
+      <c r="C12" s="24" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:5">
+      <c r="C13" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:5">
+      <c r="C14" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:5">
+      <c r="C15" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:5">
+      <c r="C16" s="24" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:5">
+      <c r="C17" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:5">
+      <c r="C18" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:5">
+      <c r="C19" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:5">
+      <c r="C20" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:5">
+      <c r="C21" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:5">
+      <c r="C22" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:5">
+      <c r="C23" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:5">
+      <c r="C24" s="24" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:5">
+      <c r="C25" s="24" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:5">
+      <c r="C26" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:5">
+      <c r="C27" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:5">
+      <c r="C28" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:5">
+      <c r="C29" s="24" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:5">
+      <c r="C30" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:5">
+      <c r="C31" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:5">
+      <c r="C32" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:5">
+      <c r="C33" s="24" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:5">
+      <c r="C34" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:5">
+      <c r="C35" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:5">
+      <c r="C36" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:5">
+      <c r="C37" s="24" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:5">
+      <c r="C38" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:5">
+      <c r="C39" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:5">
+      <c r="C40" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:5">
+      <c r="C41" s="24" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:5">
+      <c r="C42" s="24" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:5">
+      <c r="C43" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:5">
+      <c r="C44" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:5">
+      <c r="C45" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:5">
+      <c r="C46" s="24" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:5">
+      <c r="C47" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:5">
+      <c r="C48" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:5">
+      <c r="C49" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:5">
+      <c r="C50" s="24" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:5">
+      <c r="C51" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:5">
+      <c r="C52" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:5">
+      <c r="C53" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:5">
+      <c r="C54" s="24" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:5">
+      <c r="C55" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="E55" s="26" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:5">
+      <c r="C56" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="E56" s="28" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:5">
+      <c r="C57" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="E57" s="28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="通用常见问题"/>
   <dimension ref="A1:B34"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="56.4134615384615" style="1" customWidth="1"/>
-    <col min="2" max="2" width="150.528846153846" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="14" style="1"/>
+    <col min="1" max="1" width="27.3846153846154" customWidth="1"/>
+    <col min="2" max="2" width="150.528846153846" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" customHeight="1" spans="1:2">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A3" s="5"/>
-      <c r="B3" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A4" s="5"/>
-      <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A5" s="3" t="s">
+    <row r="2" customHeight="1" spans="1:2">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A13" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A15" s="12" t="s">
+      <c r="B2" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:2">
+      <c r="A3" s="7"/>
+      <c r="B3" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:2">
+      <c r="A4" s="7"/>
+      <c r="B4" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:2">
+      <c r="A5" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:2">
+      <c r="A6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A16" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A17" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A18" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A19" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="15" t="s">
+      <c r="B6" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:2">
+      <c r="A7" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:2">
+      <c r="A8" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:2">
+      <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A20" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A21" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A22" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="11" t="s">
+      <c r="B9" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:2">
+      <c r="A10" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A23" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A24" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A25" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A26" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A27" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A28" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A29" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="11" t="s">
+    <row r="11" customHeight="1" spans="1:2">
+      <c r="A11" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:2">
+      <c r="A12" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:2">
+      <c r="A13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A30" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A31" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="11" t="s">
+    <row r="14" customHeight="1" spans="1:2">
+      <c r="A14" s="8" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A32" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A33" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:2">
-      <c r="A34" s="15" t="s">
+      <c r="B14" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:2">
+      <c r="A15" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>65</v>
+      <c r="B15" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:2">
+      <c r="A16" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:2">
+      <c r="A17" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:2">
+      <c r="A18" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:2">
+      <c r="A19" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:2">
+      <c r="A20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:2">
+      <c r="A25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:2">
+      <c r="A27" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:2">
+      <c r="A28" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:2">
+      <c r="A29" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:2">
+      <c r="A30" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:2">
+      <c r="A31" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:2">
+      <c r="A32" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:2">
+      <c r="A33" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:2">
+      <c r="A34" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -2379,4 +5689,268 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="产品基础问题"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="35.7403846153846" customWidth="1"/>
+    <col min="2" max="2" width="111.413461538462" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:2">
+      <c r="A2" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:2">
+      <c r="A5" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:2">
+      <c r="A6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:2">
+      <c r="A7" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:2">
+      <c r="A8" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:2">
+      <c r="A9" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:2">
+      <c r="A12" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:2">
+      <c r="A13" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:2">
+      <c r="A14" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:2">
+      <c r="A15" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:2">
+      <c r="A16" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:2">
+      <c r="A17" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:2">
+      <c r="A18" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:2">
+      <c r="A19" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:2">
+      <c r="A20" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:2">
+      <c r="A21" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:2">
+      <c r="A22" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:2">
+      <c r="A23" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:2">
+      <c r="A24" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:2">
+      <c r="A25" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:2">
+      <c r="A26" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:2">
+      <c r="A27" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:2">
+      <c r="A28" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:2">
+      <c r="A29" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:2">
+      <c r="A30" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:2">
+      <c r="A31" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>